--- a/outputs/Block6C_Final_Uncertainty_Snapshot.xlsx
+++ b/outputs/Block6C_Final_Uncertainty_Snapshot.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="40">
   <si>
     <t>Metric</t>
   </si>
@@ -34,7 +34,10 @@
     <t>Other Popular Vote 90% Range</t>
   </si>
   <si>
-    <t>Central House Projection</t>
+    <t>House Official Central Forecast</t>
+  </si>
+  <si>
+    <t>House Monte Carlo Mean (Diagnostic)</t>
   </si>
   <si>
     <t>Democratic House 90% Range</t>
@@ -52,7 +55,10 @@
     <t>House Republican Control Probability</t>
   </si>
   <si>
-    <t>Central Senate Projection</t>
+    <t>Senate Official Central Forecast</t>
+  </si>
+  <si>
+    <t>Senate Monte Carlo Mean (Diagnostic)</t>
   </si>
   <si>
     <t>Democratic Senate 90% Range</t>
@@ -76,55 +82,58 @@
     <t>Monte Carlo Simulations</t>
   </si>
   <si>
-    <t>D 50.93% - R 46.15% - O 2.92%</t>
-  </si>
-  <si>
-    <t>48.60 – 52.20</t>
-  </si>
-  <si>
-    <t>44.28 – 47.88</t>
+    <t>D 52.07% - R 45.01% - O 2.92%</t>
+  </si>
+  <si>
+    <t>49.74 – 53.33</t>
+  </si>
+  <si>
+    <t>43.15 – 46.74</t>
   </si>
   <si>
     <t>1.52 – 3.52</t>
   </si>
   <si>
-    <t>D 224 - R 211</t>
-  </si>
-  <si>
-    <t>207 – 243</t>
-  </si>
-  <si>
-    <t>192 – 228</t>
-  </si>
-  <si>
-    <t>-21 – 51</t>
-  </si>
-  <si>
-    <t>74.58%</t>
-  </si>
-  <si>
-    <t>25.42%</t>
-  </si>
-  <si>
-    <t>D 48 - R 52</t>
-  </si>
-  <si>
-    <t>46 – 52</t>
-  </si>
-  <si>
-    <t>48 – 54</t>
-  </si>
-  <si>
-    <t>-8 – 4</t>
-  </si>
-  <si>
-    <t>22.54%</t>
-  </si>
-  <si>
-    <t>77.46%</t>
-  </si>
-  <si>
-    <t>16.12%</t>
+    <t>D 230 / R 205</t>
+  </si>
+  <si>
+    <t>D 233.46 / R 201.54</t>
+  </si>
+  <si>
+    <t>216 – 258</t>
+  </si>
+  <si>
+    <t>177 – 219</t>
+  </si>
+  <si>
+    <t>-3 – 81</t>
+  </si>
+  <si>
+    <t>92.20%</t>
+  </si>
+  <si>
+    <t>7.80%</t>
+  </si>
+  <si>
+    <t>D 50 / R 50</t>
+  </si>
+  <si>
+    <t>D 50.08 / R 49.92</t>
+  </si>
+  <si>
+    <t>47 – 53</t>
+  </si>
+  <si>
+    <t>-6 – 6</t>
+  </si>
+  <si>
+    <t>43.04%</t>
+  </si>
+  <si>
+    <t>56.96%</t>
+  </si>
+  <si>
+    <t>20.17%</t>
   </si>
 </sst>
 </file>
@@ -482,7 +491,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -498,7 +507,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -506,7 +515,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -514,7 +523,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -522,7 +531,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -530,7 +539,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -538,7 +547,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -546,7 +555,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -554,7 +563,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -562,7 +571,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -570,7 +579,7 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -578,7 +587,7 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -586,7 +595,7 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -594,7 +603,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -602,7 +611,7 @@
         <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -610,7 +619,7 @@
         <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -618,7 +627,7 @@
         <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -626,14 +635,30 @@
         <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
         <v>19</v>
       </c>
-      <c r="B19">
+      <c r="B19" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21">
         <v>50000</v>
       </c>
     </row>
